--- a/excel/PAP_Ember.xlsx
+++ b/excel/PAP_Ember.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\Downloads\Ember Releases\Ember 1.0 Stable\Ember Arquivos\Ember-arquivos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4992E6B9-B42A-421F-8E00-258DE63001E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76284AE0-D5DD-4F7E-B6E7-D137F14BE7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="137">
   <si>
     <t>DRONE</t>
   </si>
@@ -221,9 +221,6 @@
   </si>
   <si>
     <t>LM2596</t>
-  </si>
-  <si>
-    <t>Isto não está a muitas das peças que nós queimamos/não usamos ou que ficaram extra, senão daria 721,36€.</t>
   </si>
   <si>
     <t>GERAL / OUTROS</t>
@@ -447,20 +444,36 @@
     <t>Nota:</t>
   </si>
   <si>
-    <t>O motor do drone pode não ser fluido o suficiente para voar com força o suficiente, se quiseres podes dar upgrade para um motor A2216 com ESC's de 40A.</t>
-  </si>
-  <si>
     <t>Se fores fazer este upgrade, muda os valores de throttle no código principal da parte do drone.</t>
+  </si>
+  <si>
+    <t>Pilha</t>
+  </si>
+  <si>
+    <t>9V</t>
+  </si>
+  <si>
+    <t>Isto não inclui muitas das peças que nós queimamos/não usamos ou que ficaram extra, senão daria 929.40€.</t>
+  </si>
+  <si>
+    <t>O motor do drone pode não ser força o suficiente para voar (depedendo do peso), se quiseres podes dar upgrade para um motor A2216 com ESC's de 40A.</t>
+  </si>
+  <si>
+    <t>Fita Isolante</t>
+  </si>
+  <si>
+    <t>Rolo Preto</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * \-??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="m/yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -585,7 +598,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -884,28 +897,6 @@
         <color rgb="FF4B0000"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF4B0000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4B0000"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FF4B0000"/>
       </bottom>
       <diagonal/>
@@ -951,6 +942,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF4B0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4B0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4B0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -958,12 +962,12 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1085,23 +1089,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="29" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1123,7 +1122,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1141,32 +1140,36 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1474,24 +1477,24 @@
       </c>
     </row>
     <row r="3" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="73"/>
       <c r="I3" s="7"/>
-      <c r="K3" s="81" t="s">
+      <c r="K3" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
@@ -1554,15 +1557,15 @@
         <v>11</v>
       </c>
       <c r="I5" s="18"/>
-      <c r="K5" s="71" t="s">
+      <c r="K5" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
       <c r="S5" s="19"/>
       <c r="T5" s="19"/>
       <c r="U5" s="19"/>
@@ -1642,14 +1645,14 @@
         <f>SUM(E5:E16)</f>
         <v>21</v>
       </c>
-      <c r="L7" s="80" t="str">
+      <c r="L7" s="77" t="str">
         <f t="array" ref="L7">IF(COUNTA(H5:H16)=0,"---",INDEX(H5:H16,MATCH(MAX(COUNTIF(H5:H16,H5:H16)*(H5:H16&lt;&gt;"")),COUNTIF(H5:H16,H5:H16)*(H5:H16&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="80"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
       <c r="Q7" s="25">
         <f>SUMPRODUCT(E5:E16,F5:F16)</f>
         <v>266.86</v>
@@ -1705,15 +1708,15 @@
         <v>11</v>
       </c>
       <c r="I9" s="18"/>
-      <c r="K9" s="71" t="s">
+      <c r="K9" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="68"/>
+      <c r="Q9" s="68"/>
       <c r="Z9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Mauser</v>
@@ -1781,17 +1784,17 @@
         <f>SUM(E20:E31)</f>
         <v>16</v>
       </c>
-      <c r="L11" s="80" t="str">
+      <c r="L11" s="77" t="str">
         <f t="array" ref="L11">IF(COUNTA(H20:H31)=0,"---",INDEX(H20:H31,MATCH(MAX(COUNTIF(H20:H31,H20:H31)*(H20:H31&lt;&gt;"")),COUNTIF(H20:H31,H20:H31)*(H20:H31&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M11" s="80"/>
-      <c r="N11" s="80"/>
-      <c r="O11" s="80"/>
-      <c r="P11" s="80"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
       <c r="Q11" s="25">
         <f>SUMPRODUCT(E20:E31,F20:F31)</f>
-        <v>80.820000000000007</v>
+        <v>60.2</v>
       </c>
       <c r="Z11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -1843,15 +1846,15 @@
         <v>11</v>
       </c>
       <c r="I13" s="18"/>
-      <c r="K13" s="71" t="s">
+      <c r="K13" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="68"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="68"/>
+      <c r="Q13" s="68"/>
       <c r="Z13" s="5" t="str">
         <f t="shared" ref="Z13:Z24" si="1">H20</f>
         <v>Mauser</v>
@@ -1919,17 +1922,17 @@
         <f>SUM(E5:E16,E20:E31)</f>
         <v>37</v>
       </c>
-      <c r="L15" s="80" t="str">
+      <c r="L15" s="77" t="str">
         <f t="array" ref="L15">IF(COUNTA(Z1:Z26)=0,"---",INDEX(Z1:Z26,MATCH(MAX(COUNTIF(Z1:Z26,Z1:Z26)*(Z1:Z26&lt;&gt;"")),COUNTIF(Z1:Z26,Z1:Z26)*(Z1:Z26&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
       <c r="Q15" s="25">
         <f>SUMPRODUCT(E5:E16,F5:F16)+SUMPRODUCT(E20:E31,F20:F31)</f>
-        <v>347.68</v>
+        <v>327.06</v>
       </c>
       <c r="Z15" s="5" t="str">
         <f t="shared" si="1"/>
@@ -1962,29 +1965,29 @@
       </c>
     </row>
     <row r="17" spans="3:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K17" s="71" t="s">
+      <c r="K17" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
       <c r="Z17" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Escola</v>
       </c>
     </row>
     <row r="18" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C18" s="73" t="s">
+      <c r="C18" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
       <c r="I18" s="7"/>
       <c r="K18" s="20" t="s">
         <v>16</v>
@@ -2026,17 +2029,17 @@
         <f>SUM(E5:E16,E20:E31,E34:E43)</f>
         <v>58</v>
       </c>
-      <c r="L19" s="80" t="str">
+      <c r="L19" s="77" t="str">
         <f t="array" ref="L19">IF(COUNTA(Z1:Z34)=0,"---",INDEX(Z1:Z34,MATCH(MAX(COUNTIF(Z1:Z34,Z1:Z34)*(Z1:Z34&lt;&gt;"")),COUNTIF(Z1:Z34,Z1:Z34)*(Z1:Z34&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
       <c r="Q19" s="25">
-        <f>SUMPRODUCT(E5:E16,F5:F16)+SUMPRODUCT(E20:E31,F20:F31)+SUMPRODUCT(E34:E46,F34:F46)</f>
-        <v>503.05</v>
+        <f>SUMPRODUCT(E5:E16,F5:F16)+SUMPRODUCT(E20:E31,F20:F31)+SUMPRODUCT(E34:E47,F34:F47)</f>
+        <v>482.43</v>
       </c>
       <c r="Z19" s="5" t="str">
         <f t="shared" si="1"/>
@@ -2088,15 +2091,15 @@
         <v>31</v>
       </c>
       <c r="I21" s="18"/>
-      <c r="K21" s="71" t="s">
+      <c r="K21" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
       <c r="Z21" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Amazon</v>
@@ -2104,16 +2107,16 @@
     </row>
     <row r="22" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C22" s="14" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="E22" s="15">
         <v>1</v>
       </c>
       <c r="F22" s="16">
-        <v>28.96</v>
+        <v>8.34</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>10</v>
@@ -2161,19 +2164,19 @@
       </c>
       <c r="I23" s="18"/>
       <c r="K23" s="24">
-        <f>SUM(E49)</f>
+        <f>SUM(E50)</f>
         <v>2</v>
       </c>
-      <c r="L23" s="72" t="str">
-        <f>H49 &amp; T(N("Eu não preciso de uma conta inteira para isto."))</f>
+      <c r="L23" s="69" t="str">
+        <f>H50 &amp; T(N("Eu não preciso de uma conta inteira para isto."))</f>
         <v>Mauser</v>
       </c>
-      <c r="M23" s="72"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="72"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69"/>
       <c r="Q23" s="25">
-        <f>F49 + N("Nem aqui...")</f>
+        <f>F50 + N("Nem aqui...")</f>
         <v>25</v>
       </c>
       <c r="Z23" s="5" t="str">
@@ -2321,7 +2324,7 @@
       </c>
       <c r="I28" s="18"/>
       <c r="K28" s="4" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="Q28" s="37"/>
       <c r="Z28" s="5" t="str">
@@ -2393,14 +2396,14 @@
       </c>
     </row>
     <row r="32" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C32" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
-      <c r="F32" s="78"/>
-      <c r="G32" s="78"/>
-      <c r="H32" s="79"/>
+      <c r="C32" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="76"/>
       <c r="Z32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>Curto Circuito</v>
@@ -2430,10 +2433,10 @@
     </row>
     <row r="34" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C34" s="45" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="46" t="s">
         <v>64</v>
-      </c>
-      <c r="D34" s="46" t="s">
-        <v>65</v>
       </c>
       <c r="E34" s="46">
         <v>1</v>
@@ -2454,10 +2457,10 @@
     </row>
     <row r="35" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C35" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="15" t="s">
         <v>66</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>67</v>
       </c>
       <c r="E35" s="15">
         <v>1</v>
@@ -2473,16 +2476,16 @@
       </c>
       <c r="I35" s="7"/>
       <c r="Z35" s="5">
-        <f>H50</f>
+        <f>H51</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C36" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>68</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>69</v>
       </c>
       <c r="E36" s="15">
         <v>2</v>
@@ -2494,20 +2497,20 @@
         <v>10</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I36" s="13"/>
       <c r="Z36" s="5">
-        <f>H51</f>
+        <f>H52</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C37" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>71</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>72</v>
       </c>
       <c r="E37" s="15">
         <v>4</v>
@@ -2523,16 +2526,16 @@
       </c>
       <c r="I37" s="18"/>
       <c r="Z37" s="5">
-        <f>H52</f>
+        <f>H53</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>73</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="E38" s="15">
         <v>8</v>
@@ -2541,10 +2544,10 @@
         <v>3.5</v>
       </c>
       <c r="G38" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>75</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>76</v>
       </c>
       <c r="I38" s="18"/>
       <c r="Z38" s="5" t="str">
@@ -2554,10 +2557,10 @@
     </row>
     <row r="39" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C39" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>78</v>
       </c>
       <c r="E39" s="15">
         <v>1</v>
@@ -2566,23 +2569,23 @@
         <v>35.9</v>
       </c>
       <c r="G39" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>79</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>80</v>
       </c>
       <c r="I39" s="18"/>
       <c r="Z39" s="5">
-        <f>H54</f>
+        <f>H55</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C40" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>82</v>
       </c>
       <c r="E40" s="15">
         <v>1</v>
@@ -2594,20 +2597,20 @@
         <v>10</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I40" s="18"/>
       <c r="Z40" s="5">
-        <f>H55</f>
+        <f>H56</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C41" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>85</v>
       </c>
       <c r="E41" s="15">
         <v>1</v>
@@ -2619,20 +2622,20 @@
         <v>10</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I41" s="18"/>
       <c r="Z41" s="5">
-        <f>H56</f>
+        <f>H57</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C42" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="51" t="s">
         <v>86</v>
-      </c>
-      <c r="D42" s="51" t="s">
-        <v>87</v>
       </c>
       <c r="E42" s="51">
         <v>1</v>
@@ -2654,10 +2657,10 @@
     </row>
     <row r="43" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C43" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="55" t="s">
         <v>88</v>
-      </c>
-      <c r="D43" s="55" t="s">
-        <v>89</v>
       </c>
       <c r="E43" s="55">
         <v>1</v>
@@ -2669,7 +2672,7 @@
         <v>10</v>
       </c>
       <c r="H43" s="58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I43" s="18"/>
       <c r="Z43" s="5" t="str">
@@ -2679,10 +2682,10 @@
     </row>
     <row r="44" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C44" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="15" t="s">
         <v>90</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>91</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="16">
@@ -2702,10 +2705,10 @@
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.25">
       <c r="C45" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="15" t="s">
         <v>92</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>93</v>
       </c>
       <c r="E45" s="15">
         <v>1</v>
@@ -2726,22 +2729,22 @@
       </c>
     </row>
     <row r="46" spans="3:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="50" t="s">
+      <c r="C46" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" s="51">
+      <c r="E46" s="15">
         <v>1</v>
       </c>
-      <c r="F46" s="52">
+      <c r="F46" s="16">
         <v>7.68</v>
       </c>
-      <c r="G46" s="53" t="s">
+      <c r="G46" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="59" t="s">
+      <c r="H46" s="88" t="s">
         <v>31</v>
       </c>
       <c r="Z46" s="5" t="str">
@@ -2749,27 +2752,31 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="60"/>
-      <c r="D47" s="60"/>
-      <c r="E47" s="60"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="60"/>
+    <row r="47" spans="3:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="29">
+        <v>1</v>
+      </c>
+      <c r="F47" s="89">
+        <v>0</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H47" s="59" t="s">
+        <v>43</v>
+      </c>
       <c r="Z47" s="5">
         <f>H62</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C48" s="73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
+    <row r="48" spans="3:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I48" s="36"/>
       <c r="Z48" s="5">
         <f>H63</f>
@@ -2778,41 +2785,45 @@
     </row>
     <row r="49" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="36"/>
-      <c r="C49" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="E49" s="29">
-        <v>2</v>
-      </c>
-      <c r="F49" s="30">
-        <v>25</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="H49" s="62" t="s">
-        <v>11</v>
-      </c>
+      <c r="C49" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="70"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="70"/>
       <c r="I49" s="34"/>
       <c r="Z49" s="5">
         <f>H64</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="F50" s="6"/>
+    <row r="50" spans="2:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="29">
+        <v>2</v>
+      </c>
+      <c r="F50" s="30">
+        <v>25</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H50" s="59" t="s">
+        <v>11</v>
+      </c>
       <c r="Z50" s="5">
         <f>H68</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C51" s="70" t="s">
-        <v>99</v>
-      </c>
       <c r="F51" s="6"/>
       <c r="Z51" s="5">
         <f>H69</f>
@@ -2820,29 +2831,35 @@
       </c>
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C52" t="s">
-        <v>100</v>
+      <c r="C52" s="67" t="s">
+        <v>98</v>
       </c>
       <c r="F52" s="6"/>
     </row>
-    <row r="54" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C54" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="F54" s="6"/>
+    <row r="53" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C53" t="s">
+        <v>99</v>
+      </c>
+      <c r="F53" s="6"/>
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
-        <v>131</v>
+      <c r="C55" s="67" t="s">
+        <v>129</v>
       </c>
       <c r="F55" s="6"/>
-      <c r="H55" s="63"/>
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F56" s="6"/>
+      <c r="H56" s="60"/>
+    </row>
+    <row r="57" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" s="6"/>
     </row>
     <row r="62" spans="2:26" x14ac:dyDescent="0.25">
       <c r="F62" s="6"/>
@@ -2865,7 +2882,7 @@
       <c r="C67" s="36"/>
       <c r="D67" s="36"/>
       <c r="E67" s="36"/>
-      <c r="F67" s="64"/>
+      <c r="F67" s="61"/>
       <c r="G67" s="34"/>
       <c r="H67" s="36"/>
     </row>
@@ -2888,7 +2905,7 @@
   <mergeCells count="15">
     <mergeCell ref="K21:Q21"/>
     <mergeCell ref="L23:P23"/>
-    <mergeCell ref="C48:H48"/>
+    <mergeCell ref="C49:H49"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="K13:Q13"/>
@@ -2902,10 +2919,13 @@
     <mergeCell ref="K9:Q9"/>
     <mergeCell ref="L11:P11"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G16 G20:G31 G34:G46 G49:G52 G54:G56 G62:G64 G68:G72" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G16 G20:G31 G34:G46 G50:G53 G55:G57 G62:G64 G68:G72" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TIAGO,GONÇALO,AMBOS,OUTRO"</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47" xr:uid="{E232218F-1531-44F2-B271-A94DC9628499}">
+      <formula1>"TIAGO, GONÇALO, AMBOS, OUTRO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2928,403 +2948,416 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="83" t="s">
+      <c r="G2" s="84" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="82" t="s">
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="85" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="83" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65" t="s">
+      <c r="C3" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="D3" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="83"/>
-      <c r="G3" s="65" t="s">
+      <c r="E3" s="85"/>
+      <c r="G3" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="I3" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="I3" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="J3" s="83"/>
+      <c r="J3" s="85"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>1</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="64">
+        <v>45901</v>
+      </c>
+      <c r="E4" s="86" t="s">
         <v>107</v>
-      </c>
-      <c r="D4" s="67">
-        <v>45901</v>
-      </c>
-      <c r="E4" s="84" t="s">
-        <v>108</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="63" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="64">
+        <v>45901</v>
+      </c>
+      <c r="J4" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="I4" s="67">
-        <v>45901</v>
-      </c>
-      <c r="J4" s="86" t="s">
+    </row>
+    <row r="5" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="80">
+        <v>2</v>
+      </c>
+      <c r="C5" s="81" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="85">
+      <c r="D5" s="79">
+        <v>45931</v>
+      </c>
+      <c r="E5" s="86"/>
+      <c r="G5" s="80">
         <v>2</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="H5" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="79">
+        <v>45931</v>
+      </c>
+      <c r="J5" s="87"/>
+    </row>
+    <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="87"/>
+    </row>
+    <row r="7" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="80">
+        <v>3</v>
+      </c>
+      <c r="C7" s="81" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="88">
-        <v>45931</v>
-      </c>
-      <c r="E5" s="84"/>
-      <c r="G5" s="85">
-        <v>2</v>
-      </c>
-      <c r="H5" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="88">
-        <v>45931</v>
-      </c>
-      <c r="J5" s="86"/>
-    </row>
-    <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="85"/>
-      <c r="C6" s="85"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="85"/>
-      <c r="J6" s="86"/>
-    </row>
-    <row r="7" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="85">
+      <c r="D7" s="79">
+        <v>45962</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="80">
         <v>3</v>
       </c>
-      <c r="C7" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="88">
+      <c r="H7" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="79">
         <v>45962</v>
       </c>
-      <c r="E7" s="89" t="s">
-        <v>111</v>
-      </c>
-      <c r="G7" s="85">
-        <v>3</v>
-      </c>
-      <c r="H7" s="87" t="s">
+      <c r="J7" s="87"/>
+    </row>
+    <row r="8" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="80"/>
+    </row>
+    <row r="9" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="87"/>
+    </row>
+    <row r="10" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="80">
+        <v>4</v>
+      </c>
+      <c r="C10" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="88">
-        <v>45962</v>
-      </c>
-      <c r="J7" s="86"/>
-    </row>
-    <row r="8" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="85"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="85"/>
-      <c r="I8" s="85"/>
-      <c r="J8" s="85"/>
-    </row>
-    <row r="9" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="86"/>
-    </row>
-    <row r="10" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="85">
+      <c r="D10" s="79">
+        <v>45992</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="80">
         <v>4</v>
       </c>
-      <c r="C10" s="87" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="88">
+      <c r="H10" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="I10" s="79">
         <v>45992</v>
       </c>
-      <c r="E10" s="90" t="s">
+      <c r="J10" s="87"/>
+    </row>
+    <row r="11" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="80"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="80"/>
+      <c r="E11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="80"/>
+      <c r="J11" s="80"/>
+    </row>
+    <row r="12" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="80"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="83"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="87"/>
+    </row>
+    <row r="13" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="80">
+        <v>5</v>
+      </c>
+      <c r="C13" s="81" t="s">
         <v>114</v>
       </c>
-      <c r="G10" s="85">
-        <v>4</v>
-      </c>
-      <c r="H10" s="87" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="88">
-        <v>45992</v>
-      </c>
-      <c r="J10" s="86"/>
-    </row>
-    <row r="11" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-    </row>
-    <row r="12" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="90"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="86"/>
-    </row>
-    <row r="13" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="85">
+      <c r="D13" s="79">
+        <v>46023</v>
+      </c>
+      <c r="E13" s="83"/>
+      <c r="G13" s="80">
         <v>5</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="H13" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="88">
+      <c r="I13" s="79">
         <v>46023</v>
       </c>
-      <c r="E13" s="90"/>
-      <c r="G13" s="85">
-        <v>5</v>
-      </c>
-      <c r="H13" s="87" t="s">
+      <c r="J13" s="87"/>
+    </row>
+    <row r="14" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="83"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="87"/>
+    </row>
+    <row r="15" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="80">
+        <v>6</v>
+      </c>
+      <c r="C15" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="I13" s="88">
-        <v>46023</v>
-      </c>
-      <c r="J13" s="86"/>
-    </row>
-    <row r="14" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="85"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="90"/>
-      <c r="G14" s="85"/>
-      <c r="H14" s="85"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86"/>
-    </row>
-    <row r="15" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="85">
+      <c r="D15" s="79">
+        <v>46054</v>
+      </c>
+      <c r="E15" s="83"/>
+      <c r="G15" s="80">
         <v>6</v>
       </c>
-      <c r="C15" s="87" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="88">
+      <c r="H15" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="79">
         <v>46054</v>
       </c>
-      <c r="E15" s="90"/>
-      <c r="G15" s="85">
-        <v>6</v>
-      </c>
-      <c r="H15" s="87" t="s">
-        <v>116</v>
-      </c>
-      <c r="I15" s="88">
-        <v>46054</v>
-      </c>
-      <c r="J15" s="86"/>
+      <c r="J15" s="87"/>
     </row>
     <row r="16" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="85"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="90"/>
-      <c r="G16" s="85"/>
-      <c r="H16" s="85"/>
-      <c r="I16" s="85"/>
-      <c r="J16" s="86"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="80"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="83"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="87"/>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <v>7</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="67">
+      <c r="C17" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="64">
         <v>46082</v>
       </c>
-      <c r="E17" s="90"/>
+      <c r="E17" s="83"/>
       <c r="G17" s="2">
         <v>7</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" s="64">
+        <v>46082</v>
+      </c>
+      <c r="J17" s="87"/>
+    </row>
+    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="80">
+        <v>8</v>
+      </c>
+      <c r="C18" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="67">
-        <v>46082</v>
-      </c>
-      <c r="J17" s="86"/>
-    </row>
-    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="85">
+      <c r="D18" s="79">
+        <v>46113</v>
+      </c>
+      <c r="E18" s="83"/>
+      <c r="G18" s="80">
         <v>8</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="H18" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="88">
+      <c r="I18" s="79">
         <v>46113</v>
       </c>
-      <c r="E18" s="90"/>
-      <c r="G18" s="85">
-        <v>8</v>
-      </c>
-      <c r="H18" s="87" t="s">
+      <c r="J18" s="87"/>
+    </row>
+    <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="80"/>
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+    </row>
+    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="83"/>
+      <c r="G20" s="80">
+        <v>9</v>
+      </c>
+      <c r="H20" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="I18" s="88">
-        <v>46113</v>
-      </c>
-      <c r="J18" s="86"/>
-    </row>
-    <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="85"/>
-    </row>
-    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="90"/>
-      <c r="G20" s="85">
+      <c r="I20" s="79">
+        <v>46143</v>
+      </c>
+      <c r="J20" s="82" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="80">
         <v>9</v>
       </c>
-      <c r="H20" s="87" t="s">
+      <c r="C21" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="I20" s="88">
+      <c r="D21" s="79">
         <v>46143</v>
       </c>
-      <c r="J20" s="89" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="85">
-        <v>9</v>
-      </c>
-      <c r="C21" s="87" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="88">
-        <v>46143</v>
-      </c>
-      <c r="E21" s="90"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="85"/>
-      <c r="J21" s="85"/>
+      <c r="E21" s="83"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
     </row>
     <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="90"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85"/>
-      <c r="J22" s="85"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="83"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
     </row>
     <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <v>10</v>
       </c>
-      <c r="C23" s="66" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="67">
+      <c r="C23" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="64">
         <v>46174</v>
       </c>
-      <c r="E23" s="90"/>
+      <c r="E23" s="83"/>
       <c r="G23" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="64">
+        <v>46174</v>
+      </c>
+      <c r="J23" s="65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E24" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="I23" s="67">
-        <v>46174</v>
-      </c>
-      <c r="J23" s="68" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E24" s="69" t="s">
+      <c r="J24" s="66" t="s">
         <v>126</v>
-      </c>
-      <c r="J24" s="69" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="J4:J19"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="J20:J22"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="C21:C22"/>
@@ -3338,38 +3371,25 @@
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="G20:G22"/>
     <mergeCell ref="H20:H22"/>
+    <mergeCell ref="E10:E23"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
     <mergeCell ref="I7:I9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
     <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E23"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H10:H12"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="C13:C14"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="G13:G14"/>
     <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="J4:J19"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/excel/PAP_Ember.xlsx
+++ b/excel/PAP_Ember.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tiago\Downloads\Ember Releases\Ember 1.0 Stable\Ember Arquivos\Ember-arquivos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76284AE0-D5DD-4F7E-B6E7-D137F14BE7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81D3501-3EE9-4232-8D44-C999ED8326F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material" sheetId="1" r:id="rId1"/>
@@ -456,13 +456,13 @@
     <t>Isto não inclui muitas das peças que nós queimamos/não usamos ou que ficaram extra, senão daria 929.40€.</t>
   </si>
   <si>
-    <t>O motor do drone pode não ser força o suficiente para voar (depedendo do peso), se quiseres podes dar upgrade para um motor A2216 com ESC's de 40A.</t>
-  </si>
-  <si>
     <t>Fita Isolante</t>
   </si>
   <si>
     <t>Rolo Preto</t>
+  </si>
+  <si>
+    <t>O motor do drone pode não ser força o suficiente para voar (depedendo do peso), se quiseres podes dar upgrade para um motor A2216 com ESC's de 40A caso adiciones algo mais no drone.</t>
   </si>
 </sst>
 </file>
@@ -1107,6 +1107,37 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1138,37 +1169,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="26" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1477,24 +1477,24 @@
       </c>
     </row>
     <row r="3" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="73"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="84"/>
       <c r="I3" s="7"/>
-      <c r="K3" s="78" t="s">
+      <c r="K3" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
+      <c r="L3" s="89"/>
+      <c r="M3" s="89"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="89"/>
+      <c r="P3" s="89"/>
+      <c r="Q3" s="89"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
       <c r="U3" s="8"/>
@@ -1557,15 +1557,15 @@
         <v>11</v>
       </c>
       <c r="I5" s="18"/>
-      <c r="K5" s="68" t="s">
+      <c r="K5" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
       <c r="S5" s="19"/>
       <c r="T5" s="19"/>
       <c r="U5" s="19"/>
@@ -1645,14 +1645,14 @@
         <f>SUM(E5:E16)</f>
         <v>21</v>
       </c>
-      <c r="L7" s="77" t="str">
+      <c r="L7" s="88" t="str">
         <f t="array" ref="L7">IF(COUNTA(H5:H16)=0,"---",INDEX(H5:H16,MATCH(MAX(COUNTIF(H5:H16,H5:H16)*(H5:H16&lt;&gt;"")),COUNTIF(H5:H16,H5:H16)*(H5:H16&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
+      <c r="M7" s="88"/>
+      <c r="N7" s="88"/>
+      <c r="O7" s="88"/>
+      <c r="P7" s="88"/>
       <c r="Q7" s="25">
         <f>SUMPRODUCT(E5:E16,F5:F16)</f>
         <v>266.86</v>
@@ -1708,15 +1708,15 @@
         <v>11</v>
       </c>
       <c r="I9" s="18"/>
-      <c r="K9" s="68" t="s">
+      <c r="K9" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="68"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
       <c r="Z9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Mauser</v>
@@ -1784,14 +1784,14 @@
         <f>SUM(E20:E31)</f>
         <v>16</v>
       </c>
-      <c r="L11" s="77" t="str">
+      <c r="L11" s="88" t="str">
         <f t="array" ref="L11">IF(COUNTA(H20:H31)=0,"---",INDEX(H20:H31,MATCH(MAX(COUNTIF(H20:H31,H20:H31)*(H20:H31&lt;&gt;"")),COUNTIF(H20:H31,H20:H31)*(H20:H31&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="77"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
       <c r="Q11" s="25">
         <f>SUMPRODUCT(E20:E31,F20:F31)</f>
         <v>60.2</v>
@@ -1846,15 +1846,15 @@
         <v>11</v>
       </c>
       <c r="I13" s="18"/>
-      <c r="K13" s="68" t="s">
+      <c r="K13" s="79" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="68"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
       <c r="Z13" s="5" t="str">
         <f t="shared" ref="Z13:Z24" si="1">H20</f>
         <v>Mauser</v>
@@ -1922,14 +1922,14 @@
         <f>SUM(E5:E16,E20:E31)</f>
         <v>37</v>
       </c>
-      <c r="L15" s="77" t="str">
+      <c r="L15" s="88" t="str">
         <f t="array" ref="L15">IF(COUNTA(Z1:Z26)=0,"---",INDEX(Z1:Z26,MATCH(MAX(COUNTIF(Z1:Z26,Z1:Z26)*(Z1:Z26&lt;&gt;"")),COUNTIF(Z1:Z26,Z1:Z26)*(Z1:Z26&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="77"/>
+      <c r="M15" s="88"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
       <c r="Q15" s="25">
         <f>SUMPRODUCT(E5:E16,F5:F16)+SUMPRODUCT(E20:E31,F20:F31)</f>
         <v>327.06</v>
@@ -1965,29 +1965,29 @@
       </c>
     </row>
     <row r="17" spans="3:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="K17" s="68" t="s">
+      <c r="K17" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
       <c r="Z17" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Escola</v>
       </c>
     </row>
     <row r="18" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="70"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
       <c r="I18" s="7"/>
       <c r="K18" s="20" t="s">
         <v>16</v>
@@ -2029,14 +2029,14 @@
         <f>SUM(E5:E16,E20:E31,E34:E43)</f>
         <v>58</v>
       </c>
-      <c r="L19" s="77" t="str">
+      <c r="L19" s="88" t="str">
         <f t="array" ref="L19">IF(COUNTA(Z1:Z34)=0,"---",INDEX(Z1:Z34,MATCH(MAX(COUNTIF(Z1:Z34,Z1:Z34)*(Z1:Z34&lt;&gt;"")),COUNTIF(Z1:Z34,Z1:Z34)*(Z1:Z34&lt;&gt;""),0)))</f>
         <v>Mauser</v>
       </c>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="88"/>
+      <c r="O19" s="88"/>
+      <c r="P19" s="88"/>
       <c r="Q19" s="25">
         <f>SUMPRODUCT(E5:E16,F5:F16)+SUMPRODUCT(E20:E31,F20:F31)+SUMPRODUCT(E34:E47,F34:F47)</f>
         <v>482.43</v>
@@ -2091,15 +2091,15 @@
         <v>31</v>
       </c>
       <c r="I21" s="18"/>
-      <c r="K21" s="68" t="s">
+      <c r="K21" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
       <c r="Z21" s="5" t="str">
         <f t="shared" si="1"/>
         <v>Amazon</v>
@@ -2167,14 +2167,14 @@
         <f>SUM(E50)</f>
         <v>2</v>
       </c>
-      <c r="L23" s="69" t="str">
+      <c r="L23" s="80" t="str">
         <f>H50 &amp; T(N("Eu não preciso de uma conta inteira para isto."))</f>
         <v>Mauser</v>
       </c>
-      <c r="M23" s="69"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="69"/>
-      <c r="P23" s="69"/>
+      <c r="M23" s="80"/>
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
       <c r="Q23" s="25">
         <f>F50 + N("Nem aqui...")</f>
         <v>25</v>
@@ -2396,14 +2396,14 @@
       </c>
     </row>
     <row r="32" spans="3:26" x14ac:dyDescent="0.25">
-      <c r="C32" s="74" t="s">
+      <c r="C32" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="76"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="87"/>
       <c r="Z32" s="5" t="str">
         <f t="shared" si="2"/>
         <v>Curto Circuito</v>
@@ -2744,7 +2744,7 @@
       <c r="G46" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="88" t="s">
+      <c r="H46" s="68" t="s">
         <v>31</v>
       </c>
       <c r="Z46" s="5" t="str">
@@ -2754,15 +2754,15 @@
     </row>
     <row r="47" spans="3:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C47" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="D47" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="E47" s="29">
         <v>1</v>
       </c>
-      <c r="F47" s="89">
+      <c r="F47" s="69">
         <v>0</v>
       </c>
       <c r="G47" s="31" t="s">
@@ -2785,14 +2785,14 @@
     </row>
     <row r="49" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="36"/>
-      <c r="C49" s="70" t="s">
+      <c r="C49" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="70"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="70"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
       <c r="I49" s="34"/>
       <c r="Z49" s="5">
         <f>H64</f>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F56" s="6"/>
       <c r="H56" s="60"/>
@@ -2948,20 +2948,20 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="77" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="85" t="s">
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="70" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       <c r="D3" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="85"/>
+      <c r="E3" s="70"/>
       <c r="G3" s="62" t="s">
         <v>103</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="I3" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="J3" s="85"/>
+      <c r="J3" s="70"/>
     </row>
     <row r="4" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
@@ -2997,7 +2997,7 @@
       <c r="D4" s="64">
         <v>45901</v>
       </c>
-      <c r="E4" s="86" t="s">
+      <c r="E4" s="71" t="s">
         <v>107</v>
       </c>
       <c r="G4" s="2">
@@ -3009,193 +3009,193 @@
       <c r="I4" s="64">
         <v>45901</v>
       </c>
-      <c r="J4" s="87" t="s">
+      <c r="J4" s="73" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="80">
+      <c r="B5" s="72">
         <v>2</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="75">
         <v>45931</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="G5" s="80">
+      <c r="E5" s="71"/>
+      <c r="G5" s="72">
         <v>2</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="75">
         <v>45931</v>
       </c>
-      <c r="J5" s="87"/>
+      <c r="J5" s="73"/>
     </row>
     <row r="6" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="87"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72"/>
+      <c r="E6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="73"/>
     </row>
     <row r="7" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="80">
+      <c r="B7" s="72">
         <v>3</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="74" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="75">
         <v>45962</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="76" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="80">
+      <c r="G7" s="72">
         <v>3</v>
       </c>
-      <c r="H7" s="81" t="s">
+      <c r="H7" s="74" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="75">
         <v>45962</v>
       </c>
-      <c r="J7" s="87"/>
+      <c r="J7" s="73"/>
     </row>
     <row r="8" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
-      <c r="J8" s="80"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
     </row>
     <row r="9" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="87"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="73"/>
     </row>
     <row r="10" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="80">
+      <c r="B10" s="72">
         <v>4</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="75">
         <v>45992</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="80">
+      <c r="G10" s="72">
         <v>4</v>
       </c>
-      <c r="H10" s="81" t="s">
+      <c r="H10" s="74" t="s">
         <v>112</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="75">
         <v>45992</v>
       </c>
-      <c r="J10" s="87"/>
+      <c r="J10" s="73"/>
     </row>
     <row r="11" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="80"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="72"/>
+      <c r="G11" s="72"/>
+      <c r="H11" s="72"/>
+      <c r="I11" s="72"/>
+      <c r="J11" s="72"/>
     </row>
     <row r="12" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="83"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="87"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="78"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="73"/>
     </row>
     <row r="13" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="80">
+      <c r="B13" s="72">
         <v>5</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="75">
         <v>46023</v>
       </c>
-      <c r="E13" s="83"/>
-      <c r="G13" s="80">
+      <c r="E13" s="78"/>
+      <c r="G13" s="72">
         <v>5</v>
       </c>
-      <c r="H13" s="81" t="s">
+      <c r="H13" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="I13" s="79">
+      <c r="I13" s="75">
         <v>46023</v>
       </c>
-      <c r="J13" s="87"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="83"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="87"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="78"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="73"/>
     </row>
     <row r="15" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="80">
+      <c r="B15" s="72">
         <v>6</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="75">
         <v>46054</v>
       </c>
-      <c r="E15" s="83"/>
-      <c r="G15" s="80">
+      <c r="E15" s="78"/>
+      <c r="G15" s="72">
         <v>6</v>
       </c>
-      <c r="H15" s="81" t="s">
+      <c r="H15" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="I15" s="79">
+      <c r="I15" s="75">
         <v>46054</v>
       </c>
-      <c r="J15" s="87"/>
+      <c r="J15" s="73"/>
     </row>
     <row r="16" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="80"/>
-      <c r="C16" s="80"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="83"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="87"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="78"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="73"/>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
@@ -3207,7 +3207,7 @@
       <c r="D17" s="64">
         <v>46082</v>
       </c>
-      <c r="E17" s="83"/>
+      <c r="E17" s="78"/>
       <c r="G17" s="2">
         <v>7</v>
       </c>
@@ -3217,83 +3217,83 @@
       <c r="I17" s="64">
         <v>46082</v>
       </c>
-      <c r="J17" s="87"/>
+      <c r="J17" s="73"/>
     </row>
     <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="80">
+      <c r="B18" s="72">
         <v>8</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="79">
+      <c r="D18" s="75">
         <v>46113</v>
       </c>
-      <c r="E18" s="83"/>
-      <c r="G18" s="80">
+      <c r="E18" s="78"/>
+      <c r="G18" s="72">
         <v>8</v>
       </c>
-      <c r="H18" s="81" t="s">
+      <c r="H18" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="I18" s="79">
+      <c r="I18" s="75">
         <v>46113</v>
       </c>
-      <c r="J18" s="87"/>
+      <c r="J18" s="73"/>
     </row>
     <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="80"/>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
     </row>
     <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="83"/>
-      <c r="G20" s="80">
+      <c r="B20" s="72"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="78"/>
+      <c r="G20" s="72">
         <v>9</v>
       </c>
-      <c r="H20" s="81" t="s">
+      <c r="H20" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="I20" s="79">
+      <c r="I20" s="75">
         <v>46143</v>
       </c>
-      <c r="J20" s="82" t="s">
+      <c r="J20" s="76" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="80">
+      <c r="B21" s="72">
         <v>9</v>
       </c>
-      <c r="C21" s="81" t="s">
+      <c r="C21" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="75">
         <v>46143</v>
       </c>
-      <c r="E21" s="83"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
+      <c r="E21" s="78"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="72"/>
     </row>
     <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="83"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="78"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
     </row>
     <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
@@ -3305,7 +3305,7 @@
       <c r="D23" s="64">
         <v>46174</v>
       </c>
-      <c r="E23" s="83"/>
+      <c r="E23" s="78"/>
       <c r="G23" s="2">
         <v>10</v>
       </c>
@@ -3339,6 +3339,41 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="I10:I12"/>
+    <mergeCell ref="E10:E23"/>
+    <mergeCell ref="G10:G12"/>
+    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="I20:I22"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="H20:H22"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="J4:J19"/>
@@ -3355,41 +3390,6 @@
     <mergeCell ref="I13:I14"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="G15:G16"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="E10:E23"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="I20:I22"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="I10:I12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:H14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
